--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486672_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486672_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.585</v>
+        <v>3.4263</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1857</v>
+        <v>0.2832</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7707</v>
+        <v>3.1432</v>
       </c>
       <c r="G2" t="n">
         <v>3.4337</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4067</v>
+        <v>-0.5653</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8829</v>
+        <v>-0.414</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5238</v>
+        <v>-0.1513</v>
       </c>
       <c r="V2" t="n">
         <v>0.3649</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4722</v>
+        <v>1.0378</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4684</v>
+        <v>2.1582</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9962</v>
+        <v>-1.1204</v>
       </c>
       <c r="G3" t="n">
         <v>5.3152</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5241</v>
+        <v>0.0897</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1375</v>
+        <v>-0.1727</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3866</v>
+        <v>0.2624</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5056</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1298</v>
+        <v>-0.259</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2755</v>
+        <v>0.8618</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1456</v>
+        <v>-1.1208</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2761</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9542</v>
+        <v>0.5653</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2134</v>
+        <v>0.7997</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5482</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8942</v>
+        <v>-1.1492</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0554</v>
+        <v>-0.1997</v>
       </c>
       <c r="F5" t="n">
         <v>-0.9496</v>
@@ -844,10 +844,10 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3586</v>
+        <v>-0.6137</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.3382</v>
       </c>
       <c r="U5" t="n">
         <v>-0.2756</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.18</v>
+        <v>-1.2653</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8645</v>
+        <v>-1.223</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3155</v>
+        <v>-0.0423</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2713</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2369</v>
+        <v>0.1516</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6063</v>
+        <v>0.2478</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3694</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>2.0129</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7771</v>
+        <v>-1.8639</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3572</v>
+        <v>0.0469</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1343</v>
+        <v>-1.9108</v>
       </c>
       <c r="G7" t="n">
         <v>-4.5599</v>
@@ -1000,13 +1000,13 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3969</v>
+        <v>0.3101</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4684</v>
+        <v>0.1581</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07149999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="V7" t="n">
         <v>2.1928</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9888</v>
+        <v>-2.9143</v>
       </c>
       <c r="E8" t="n">
         <v>-1.7354</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2534</v>
+        <v>-1.1789</v>
       </c>
       <c r="G8" t="n">
         <v>-0.585</v>
@@ -1078,13 +1078,13 @@
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5736</v>
+        <v>0.6481</v>
       </c>
       <c r="T8" t="n">
         <v>0.1927</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3809</v>
+        <v>0.4554</v>
       </c>
       <c r="V8" t="n">
         <v>1.2703</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0936</v>
+        <v>-3.4093</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0143</v>
+        <v>-3.5402</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9207</v>
+        <v>0.1309</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6291</v>
+        <v>-1.609</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.8687</v>
+        <v>-1.4688</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2396</v>
+        <v>-0.1402</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2006</v>
+        <v>-0.6768</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.282</v>
+        <v>-0.6407</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0814</v>
+        <v>-0.0361</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4285</v>
+        <v>-0.9322</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5867</v>
+        <v>-0.8282</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1582</v>
+        <v>-0.1041</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5446</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3169</v>
+        <v>-2.1239</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4236</v>
+        <v>-0.7517</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4968</v>
+        <v>-0.6969</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9204</v>
+        <v>-0.0548</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6565</v>
+        <v>-0.6624</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6565</v>
+        <v>-0.6198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0312</v>
+        <v>-3.7103</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1125</v>
+        <v>-4.9109</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.2006</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.609</v>
+        <v>-3.6291</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4688</v>
+        <v>-3.8687</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1402</v>
+        <v>0.2396</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6768</v>
+        <v>-2.2006</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6407</v>
+        <v>-2.282</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0361</v>
+        <v>0.0814</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9322</v>
+        <v>-1.4285</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8282</v>
+        <v>-1.5867</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1041</v>
+        <v>0.1582</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1239</v>
+        <v>-2.3169</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3736</v>
+        <v>0.8069</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2692</v>
+        <v>-0.3933</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1044</v>
+        <v>1.2003</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6624</v>
+        <v>0.6565</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6198</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.2108</v>
+        <v>-6.6055</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0489</v>
+        <v>-6.2698</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1619</v>
+        <v>-0.3357</v>
       </c>
       <c r="G11" t="n">
         <v>-6.8013</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4192</v>
+        <v>0.1861</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8554</v>
+        <v>-0.0762</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4362</v>
+        <v>0.2624</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3419</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.9887</v>
+        <v>-16.7127</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.8048</v>
+        <v>-14.5289</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1839</v>
+        <v>-2.1838</v>
       </c>
       <c r="G12" t="n">
         <v>-10.6205</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.2406</v>
+        <v>-7.240600000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-3.379900000000001</v>
@@ -1378,10 +1378,10 @@
         <v>-10.6946</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4188000000000002</v>
+        <v>-0.4188000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-8.688600000000001</v>
+        <v>-8.688599999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-21.2385</v>
@@ -1390,16 +1390,16 @@
         <v>12.55</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5511999999999999</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9691000000000002</v>
+        <v>-0.6930000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>1.5202</v>
       </c>
       <c r="V12" t="n">
-        <v>1.769100000000001</v>
+        <v>1.7691</v>
       </c>
       <c r="W12" t="n">
         <v>6.910099999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1736</v>
+        <v>5.1268</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0715</v>
+        <v>1.451</v>
       </c>
       <c r="F13" t="n">
-        <v>3.102</v>
+        <v>3.6758</v>
       </c>
       <c r="G13" t="n">
         <v>2.7478</v>
@@ -1468,13 +1468,13 @@
         <v>3.2823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0774</v>
+        <v>-0.1241</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4132</v>
+        <v>-0.2073</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4906</v>
+        <v>0.0832</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7792</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6355</v>
+        <v>4.1464</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8636</v>
+        <v>3.5092</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7718</v>
+        <v>0.6372</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6401</v>
+        <v>3.7465</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.524</v>
+        <v>2.2138</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8839</v>
+        <v>1.5328</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5844</v>
+        <v>4.8924</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3169</v>
+        <v>2.973</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7325</v>
+        <v>1.9194</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0557</v>
+        <v>-1.1459</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2071</v>
+        <v>-0.7593</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1514</v>
+        <v>-0.3866</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4839</v>
+        <v>0.4345</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9927</v>
+        <v>-0.3519</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4912</v>
+        <v>0.7864</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8262</v>
+        <v>-0.6138</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4554</v>
+        <v>0.8995</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3709</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4348</v>
+        <v>3.8748</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4057</v>
+        <v>0.992</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0291</v>
+        <v>2.8828</v>
       </c>
       <c r="G15" t="n">
         <v>0.6487000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>3.2823</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6771</v>
+        <v>1.1171</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5236</v>
+        <v>0.1099</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1535</v>
+        <v>1.0072</v>
       </c>
       <c r="V15" t="n">
         <v>-0.208</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4748</v>
+        <v>3.7377</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1989</v>
+        <v>2.1397</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2758</v>
+        <v>1.598</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7465</v>
+        <v>-0.6401</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2138</v>
+        <v>-1.524</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5328</v>
+        <v>0.8839</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8924</v>
+        <v>-0.5844</v>
       </c>
       <c r="K16" t="n">
-        <v>2.973</v>
+        <v>-1.3169</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9194</v>
+        <v>0.7325</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1459</v>
+        <v>-0.0557</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7593</v>
+        <v>-0.2071</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3866</v>
+        <v>0.1514</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.51</v>
+        <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2372</v>
+        <v>0.5861</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6622</v>
+        <v>0.2687</v>
       </c>
       <c r="U16" t="n">
-        <v>0.425</v>
+        <v>0.3174</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6138</v>
+        <v>2.8262</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8995</v>
+        <v>2.4554</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5133</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4937</v>
+        <v>2.5486</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9174</v>
+        <v>-0.5038</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4111</v>
+        <v>3.0524</v>
       </c>
       <c r="G17" t="n">
         <v>0.7691</v>
@@ -1780,13 +1780,13 @@
         <v>3.0892</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4692</v>
+        <v>0.5242</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8554</v>
+        <v>-0.4417</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3246</v>
+        <v>0.9659</v>
       </c>
       <c r="V17" t="n">
         <v>1.0623</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5036</v>
+        <v>1.9614</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1771</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6807</v>
+        <v>2.9317</v>
       </c>
       <c r="G18" t="n">
         <v>1.5503</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4026</v>
+        <v>0.0552</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6622</v>
+        <v>-0.4553</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2596</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0.1628</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8277</v>
+        <v>1.4897</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5585</v>
+        <v>-1.1449</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3862</v>
+        <v>2.6345</v>
       </c>
       <c r="G19" t="n">
         <v>2.8617</v>
@@ -1936,13 +1936,13 @@
         <v>2.7031</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4894</v>
+        <v>-0.8274</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9657</v>
+        <v>-0.5521</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.2754</v>
       </c>
       <c r="V19" t="n">
         <v>0.6138</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7299</v>
+        <v>1.1395</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8781</v>
+        <v>1.1884</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1482</v>
+        <v>-0.0488</v>
       </c>
       <c r="G20" t="n">
         <v>2.8485</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0992</v>
+        <v>0.3104</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0828</v>
+        <v>0.2274</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0164</v>
+        <v>0.083</v>
       </c>
       <c r="V20" t="n">
         <v>-2.2124</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6219</v>
+        <v>0.1337</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9406</v>
+        <v>0.5269</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3187</v>
+        <v>-0.3932</v>
       </c>
       <c r="G21" t="n">
         <v>0.0273</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.309</v>
+        <v>-0.1792</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6343</v>
+        <v>0.2206</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3253</v>
+        <v>-0.3998</v>
       </c>
       <c r="V21" t="n">
         <v>0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2858</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7792</v>
+        <v>-0.6757</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.2694</v>
       </c>
       <c r="G22" t="n">
         <v>0.5653</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2026</v>
+        <v>-0.862</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4415</v>
+        <v>-0.338</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7612</v>
+        <v>-0.5239</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4015</v>
+        <v>-1.4553</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2274</v>
+        <v>-0.3308</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1742</v>
+        <v>-1.1245</v>
       </c>
       <c r="G23" t="n">
         <v>-1.924</v>
@@ -2248,13 +2248,13 @@
         <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5033</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4688</v>
+        <v>0.3653</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0883</v>
+        <v>0.138</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2193</v>
+        <v>-3.3905</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5149</v>
+        <v>-3.9978</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2955</v>
+        <v>0.6073</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5808</v>
@@ -2326,13 +2326,13 @@
         <v>1.9308</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5391</v>
+        <v>-0.7103</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8829</v>
+        <v>-0.3658</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6562</v>
+        <v>-0.3445</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0648</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.9889</v>
+        <v>18.3677</v>
       </c>
       <c r="E25" t="n">
-        <v>2.183899999999999</v>
+        <v>2.183900000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>14.8045</v>
+        <v>16.1838</v>
       </c>
       <c r="G25" t="n">
         <v>10.6203</v>
@@ -2404,13 +2404,13 @@
         <v>21.2385</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5512999999999998</v>
+        <v>0.8277999999999995</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5201</v>
+        <v>-1.5202</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9687999999999998</v>
+        <v>2.348100000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-1.769</v>
